--- a/artfynd/A 14353-2026 artfynd.xlsx
+++ b/artfynd/A 14353-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>65999863</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572912.4547728549</v>
+        <v>572912</v>
       </c>
       <c r="R2" t="n">
-        <v>6848974.239525061</v>
+        <v>6848974</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,19 +745,9 @@
           <t>2017-05-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-05-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,6 +772,130 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>65999866</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>S Järnvallssjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>572858</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6848946</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Delsbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-05-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-05-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
